--- a/BWI/bestwine_output/bestwine_Ukraine.xlsx
+++ b/BWI/bestwine_output/bestwine_Ukraine.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA96"/>
+  <dimension ref="A1:AA100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -10698,6 +10698,378 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Varus</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>168601</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Dnipro</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>11Б Oleksandra Polia Ave</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>49000</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>https://varus.ua</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>support@varus.ua</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>+380 800 307 080</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr"/>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/varusua/</t>
+        </is>
+      </c>
+      <c r="S97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61568321954685</t>
+        </is>
+      </c>
+      <c r="T97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/varus.ua/</t>
+        </is>
+      </c>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/varus_ukraine</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr"/>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>Nazely Yengoyan</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>Import and Purchasing Manager – Wine &amp; Spirits Category</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr"/>
+      <c r="Z97" s="2" t="inlineStr"/>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/nazely-yengoyan-677242126</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Varus</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>168601</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Dnipro</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>11Б Oleksandra Polia Ave</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>49000</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>https://varus.ua</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>support@varus.ua</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>+380 800 307 080</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr"/>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/varusua/</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61568321954685</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/varus.ua/</t>
+        </is>
+      </c>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/varus_ukraine</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr"/>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>Alona Lambrakis</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>Import Manager</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr"/>
+      <c r="Z98" s="2" t="inlineStr"/>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/alona-lambrakis-a98777178</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Varus</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>168601</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Dnipro</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>11Б Oleksandra Polia Ave</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>49000</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>https://varus.ua</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>support@varus.ua</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>+380 800 307 080</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr"/>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/varusua/</t>
+        </is>
+      </c>
+      <c r="S99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61568321954685</t>
+        </is>
+      </c>
+      <c r="T99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/varus.ua/</t>
+        </is>
+      </c>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/varus_ukraine</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr"/>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>Oleksandra Tishchenko</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Manager</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr"/>
+      <c r="Z99" s="2" t="inlineStr"/>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/oleksandra-tishchenko-a39465204</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Varus</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>168601</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Dnipro</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>11Б Oleksandra Polia Ave</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>49000</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>https://varus.ua</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>support@varus.ua</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>+380 800 307 080</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/varusua/</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61568321954685</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/varus.ua/</t>
+        </is>
+      </c>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/varus_ukraine</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr"/>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>Viktoriia Volynets</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Manager</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr"/>
+      <c r="Z100" s="2" t="inlineStr"/>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/viktoriia-volynets-5b141a248</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Ukraine.xlsx
+++ b/BWI/bestwine_output/bestwine_Ukraine.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA100"/>
+  <dimension ref="A1:AA101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -11070,6 +11070,83 @@
         </is>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Invino Direct</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Invino Direct</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>65106</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Kharkiv</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Kharkivs'ka oblast, Kharkivs'ka city council</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>54 Myronosytska Street</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>61000</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>https://invino.com.ua</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>ishop@invino.com.ua</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr"/>
+      <c r="P101" s="2" t="inlineStr"/>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/invinomir/</t>
+        </is>
+      </c>
+      <c r="T101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/invino_profi/</t>
+        </is>
+      </c>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr"/>
+      <c r="W101" s="2" t="inlineStr"/>
+      <c r="X101" s="2" t="inlineStr"/>
+      <c r="Y101" s="2" t="inlineStr"/>
+      <c r="Z101" s="2" t="inlineStr"/>
+      <c r="AA101" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Ukraine.xlsx
+++ b/BWI/bestwine_output/bestwine_Ukraine.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA101"/>
+  <dimension ref="A1:AA110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -11147,6 +11147,755 @@
       <c r="Z101" s="2" t="inlineStr"/>
       <c r="AA101" s="2" t="inlineStr"/>
     </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Shevchenko Trading House Llc</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Shevchenko Trading House Llc</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>55290</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Dnipro</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Dnipropetrovsk Oblast, Dnipropetrovs'ka city council</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>St. Nizhnedneprovskaya, 1/zh</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>49000</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>https://alcomag.ua</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>info@alcomag.com.ua</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr"/>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>2577522030</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/alcomag.ua/</t>
+        </is>
+      </c>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/alcomag_ua</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr"/>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>Ihor Akatyev</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr"/>
+      <c r="Z102" s="2" t="inlineStr"/>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ihor-akatyev-616591287</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Tf Style</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Tf Style</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>49630</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Kalush</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Ivano-Frankivsk Oblast, Kalus'ka city council</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Karakaya Str., 26zh</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>77300</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>http://style.if.ua</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>info@style.if.ua</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>+380 3472 62993</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>38472641</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr"/>
+      <c r="V103" s="2" t="inlineStr"/>
+      <c r="W103" s="2" t="inlineStr"/>
+      <c r="X103" s="2" t="inlineStr"/>
+      <c r="Y103" s="2" t="inlineStr"/>
+      <c r="Z103" s="2" t="inlineStr"/>
+      <c r="AA103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Wine &amp; Food Kiev</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Wine &amp; Food Kiev</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>55443</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Kyiv</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Kyiv City</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>13 Shovkovychna Street</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>01021</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>https://winefood.ua</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>wineandfood.kiev@gmail.com</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr"/>
+      <c r="P104" s="2" t="inlineStr"/>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr"/>
+      <c r="V104" s="2" t="inlineStr"/>
+      <c r="W104" s="2" t="inlineStr"/>
+      <c r="X104" s="2" t="inlineStr"/>
+      <c r="Y104" s="2" t="inlineStr"/>
+      <c r="Z104" s="2" t="inlineStr"/>
+      <c r="AA104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Pivasov</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Pivasov</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>65328</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Odesa</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Odes'ka oblast, Odes'ka city council</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>49 Henerala Petrova Street</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>65000</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>https://pivasov.ua</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>office@pivasov.ua</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr"/>
+      <c r="P105" s="2" t="inlineStr"/>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/pivasov.ua</t>
+        </is>
+      </c>
+      <c r="T105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pivasov.ua/</t>
+        </is>
+      </c>
+      <c r="U105" s="2" t="inlineStr"/>
+      <c r="V105" s="2" t="inlineStr"/>
+      <c r="W105" s="2" t="inlineStr"/>
+      <c r="X105" s="2" t="inlineStr"/>
+      <c r="Y105" s="2" t="inlineStr"/>
+      <c r="Z105" s="2" t="inlineStr"/>
+      <c r="AA105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Vino &amp; Vino</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Vino &amp; Vino</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>49522</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Kyiv</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Kyiv, Kyiv City</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>47 Sichovykh Striltsiv Street</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>02000</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>https://vinovino.com.ua</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>info@vinovino.com.ua</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>+380 800 207 629</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr"/>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinovino.ukraine/</t>
+        </is>
+      </c>
+      <c r="T106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinovino.com.ua</t>
+        </is>
+      </c>
+      <c r="U106" s="2" t="inlineStr"/>
+      <c r="V106" s="2" t="inlineStr"/>
+      <c r="W106" s="2" t="inlineStr"/>
+      <c r="X106" s="2" t="inlineStr"/>
+      <c r="Y106" s="2" t="inlineStr"/>
+      <c r="Z106" s="2" t="inlineStr"/>
+      <c r="AA106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Vinhol Velvet</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Vinhol Velvet</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>51810</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Odessa</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Odeska</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>St. New 1-b, Oksamitnoe</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>65031</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>https://winehall.prom.ua</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>winehall2006@gmail.com</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr"/>
+      <c r="P107" s="2" t="inlineStr"/>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winehall-oksamytne/</t>
+        </is>
+      </c>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr"/>
+      <c r="V107" s="2" t="inlineStr"/>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>Tintulov Yuriy</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Manager</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr"/>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tintulov-yuriy-b79ab515a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Vinhol Velvet</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Vinhol Velvet</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>51810</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Odessa</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Odeska</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>St. New 1-b, Oksamitnoe</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>65031</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>https://winehall.prom.ua</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>winehall2006@gmail.com</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr"/>
+      <c r="P108" s="2" t="inlineStr"/>
+      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="R108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winehall-oksamytne/</t>
+        </is>
+      </c>
+      <c r="S108" s="2" t="inlineStr"/>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr"/>
+      <c r="V108" s="2" t="inlineStr"/>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dmitry </t>
+        </is>
+      </c>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr"/>
+      <c r="Z108" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Vinhol Velvet</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Vinhol Velvet</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>51810</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Odessa</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Odeska</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>St. New 1-b, Oksamitnoe</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>65031</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>https://winehall.prom.ua</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr"/>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>winehall2006@gmail.com</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr"/>
+      <c r="P109" s="2" t="inlineStr"/>
+      <c r="Q109" s="2" t="inlineStr"/>
+      <c r="R109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winehall-oksamytne/</t>
+        </is>
+      </c>
+      <c r="S109" s="2" t="inlineStr"/>
+      <c r="T109" s="2" t="inlineStr"/>
+      <c r="U109" s="2" t="inlineStr"/>
+      <c r="V109" s="2" t="inlineStr"/>
+      <c r="W109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Constantine </t>
+        </is>
+      </c>
+      <c r="X109" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y109" s="2" t="inlineStr"/>
+      <c r="Z109" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Invino Direct</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Invino Direct</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>65106</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Kharkiv</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Kharkivs'ka oblast, Kharkivs'ka city council</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>54 Myronosytska Street</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>61000</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>https://invino.com.ua</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>ishop@invino.com.ua</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr"/>
+      <c r="P110" s="2" t="inlineStr"/>
+      <c r="Q110" s="2" t="inlineStr"/>
+      <c r="R110" s="2" t="inlineStr"/>
+      <c r="S110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/invinomir/</t>
+        </is>
+      </c>
+      <c r="T110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/invino_profi/</t>
+        </is>
+      </c>
+      <c r="U110" s="2" t="inlineStr"/>
+      <c r="V110" s="2" t="inlineStr"/>
+      <c r="W110" s="2" t="inlineStr"/>
+      <c r="X110" s="2" t="inlineStr"/>
+      <c r="Y110" s="2" t="inlineStr"/>
+      <c r="Z110" s="2" t="inlineStr"/>
+      <c r="AA110" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Ukraine.xlsx
+++ b/BWI/bestwine_output/bestwine_Ukraine.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA110"/>
+  <dimension ref="A1:AA124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -11896,6 +11896,1192 @@
       <c r="Z110" s="2" t="inlineStr"/>
       <c r="AA110" s="2" t="inlineStr"/>
     </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Winestyle.com.ua</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Winestyle.com.ua</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>39891</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Vyshneve</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Kyivs'ka oblast, Kyjevo-Svyatoshyns'kyi district</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>31 vulytsia Mashynobudivnykiv</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>08132</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>https://winestyle.com.ua</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr"/>
+      <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="2" t="inlineStr"/>
+      <c r="M111" s="2" t="inlineStr"/>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>sales@winestyle.com.ua</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr"/>
+      <c r="P111" s="2" t="inlineStr"/>
+      <c r="Q111" s="2" t="inlineStr"/>
+      <c r="R111" s="2" t="inlineStr"/>
+      <c r="S111" s="2" t="inlineStr"/>
+      <c r="T111" s="2" t="inlineStr"/>
+      <c r="U111" s="2" t="inlineStr"/>
+      <c r="V111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@wine_style</t>
+        </is>
+      </c>
+      <c r="W111" s="2" t="inlineStr"/>
+      <c r="X111" s="2" t="inlineStr"/>
+      <c r="Y111" s="2" t="inlineStr"/>
+      <c r="Z111" s="2" t="inlineStr"/>
+      <c r="AA111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Alkomir</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Alkomir</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>117761</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Kyiv</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Kyiv, Kyiv City</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>26 Elektrykiv Street</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>04176</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>https://alkomir.com.ua</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="2" t="inlineStr"/>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>info@alkomir.com.ua</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr"/>
+      <c r="P112" s="2" t="inlineStr"/>
+      <c r="Q112" s="2" t="inlineStr"/>
+      <c r="R112" s="2" t="inlineStr"/>
+      <c r="S112" s="2" t="inlineStr"/>
+      <c r="T112" s="2" t="inlineStr"/>
+      <c r="U112" s="2" t="inlineStr"/>
+      <c r="V112" s="2" t="inlineStr"/>
+      <c r="W112" s="2" t="inlineStr"/>
+      <c r="X112" s="2" t="inlineStr"/>
+      <c r="Y112" s="2" t="inlineStr"/>
+      <c r="Z112" s="2" t="inlineStr"/>
+      <c r="AA112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Ekspansiya, Tov</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Ekspansiya, Tov</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>55387</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Kyiv</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Kyiv city, Kyiv City</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Ave. Pavla Tychyna, 1-b</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>02000</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fozzy.ua</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr"/>
+      <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr"/>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>realty@fozzy.ua</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>+380 44 593 0377</t>
+        </is>
+      </c>
+      <c r="P113" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q113" s="2" t="inlineStr">
+        <is>
+          <t>32294905</t>
+        </is>
+      </c>
+      <c r="R113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fozzy-group/</t>
+        </is>
+      </c>
+      <c r="S113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/fozzygroup</t>
+        </is>
+      </c>
+      <c r="T113" s="2" t="inlineStr"/>
+      <c r="U113" s="2" t="inlineStr"/>
+      <c r="V113" s="2" t="inlineStr"/>
+      <c r="W113" s="2" t="inlineStr">
+        <is>
+          <t>Tsyhanii Serhii</t>
+        </is>
+      </c>
+      <c r="X113" s="2" t="inlineStr">
+        <is>
+          <t>Import Manager</t>
+        </is>
+      </c>
+      <c r="Y113" s="2" t="inlineStr"/>
+      <c r="Z113" s="2" t="inlineStr"/>
+      <c r="AA113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tsyhanii-serhii-0a7620213/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Ekspansiya, Tov</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Ekspansiya, Tov</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>55387</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Kyiv</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Kyiv city, Kyiv City</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Ave. Pavla Tychyna, 1-b</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>02000</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fozzy.ua</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr"/>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>realty@fozzy.ua</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>+380 44 593 0377</t>
+        </is>
+      </c>
+      <c r="P114" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q114" s="2" t="inlineStr">
+        <is>
+          <t>32294905</t>
+        </is>
+      </c>
+      <c r="R114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fozzy-group/</t>
+        </is>
+      </c>
+      <c r="S114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/fozzygroup</t>
+        </is>
+      </c>
+      <c r="T114" s="2" t="inlineStr"/>
+      <c r="U114" s="2" t="inlineStr"/>
+      <c r="V114" s="2" t="inlineStr"/>
+      <c r="W114" s="2" t="inlineStr">
+        <is>
+          <t>Anna Pushkina</t>
+        </is>
+      </c>
+      <c r="X114" s="2" t="inlineStr">
+        <is>
+          <t>Senior Import Manager</t>
+        </is>
+      </c>
+      <c r="Y114" s="2" t="inlineStr"/>
+      <c r="Z114" s="2" t="inlineStr"/>
+      <c r="AA114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anna-pushkina-4a5343b7/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Beer Market</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Beer Market</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>46023</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Harkiv</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Harkov</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Stadionnyi Proizd, 13</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>‎61001</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>https://beer-market.com.ua</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr"/>
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr"/>
+      <c r="M115" s="2" t="inlineStr"/>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>info@beer-market.com.ua</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>+380 800 502 506</t>
+        </is>
+      </c>
+      <c r="P115" s="2" t="inlineStr"/>
+      <c r="Q115" s="2" t="inlineStr"/>
+      <c r="R115" s="2" t="inlineStr"/>
+      <c r="S115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/BeerMarketUA/</t>
+        </is>
+      </c>
+      <c r="T115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/beermarket_ua</t>
+        </is>
+      </c>
+      <c r="U115" s="2" t="inlineStr"/>
+      <c r="V115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@beermarket5513</t>
+        </is>
+      </c>
+      <c r="W115" s="2" t="inlineStr"/>
+      <c r="X115" s="2" t="inlineStr"/>
+      <c r="Y115" s="2" t="inlineStr"/>
+      <c r="Z115" s="2" t="inlineStr"/>
+      <c r="AA115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Shevchenko Trading House Llc</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Shevchenko Trading House Llc</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>55290</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Dnipro</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Dnipropetrovsk Oblast, Dnipropetrovs'ka city council</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>St. Nizhnedneprovskaya, 1/zh</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>49000</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>https://alcomag.ua</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr"/>
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr"/>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>info@alcomag.com.ua</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr"/>
+      <c r="P116" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q116" s="2" t="inlineStr">
+        <is>
+          <t>2577522030</t>
+        </is>
+      </c>
+      <c r="R116" s="2" t="inlineStr"/>
+      <c r="S116" s="2" t="inlineStr"/>
+      <c r="T116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/alcomag.ua/</t>
+        </is>
+      </c>
+      <c r="U116" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/alcomag_ua</t>
+        </is>
+      </c>
+      <c r="V116" s="2" t="inlineStr"/>
+      <c r="W116" s="2" t="inlineStr">
+        <is>
+          <t>Ihor Akatyev</t>
+        </is>
+      </c>
+      <c r="X116" s="2" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="Y116" s="2" t="inlineStr"/>
+      <c r="Z116" s="2" t="inlineStr"/>
+      <c r="AA116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ihor-akatyev-616591287</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Tf Style</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Tf Style</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>49630</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Kalush</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Ivano-Frankivsk Oblast, Kalus'ka city council</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>Karakaya Str., 26zh</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>77300</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>http://style.if.ua</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr"/>
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr"/>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>info@style.if.ua</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>+380 3472 62993</t>
+        </is>
+      </c>
+      <c r="P117" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q117" s="2" t="inlineStr">
+        <is>
+          <t>38472641</t>
+        </is>
+      </c>
+      <c r="R117" s="2" t="inlineStr"/>
+      <c r="S117" s="2" t="inlineStr"/>
+      <c r="T117" s="2" t="inlineStr"/>
+      <c r="U117" s="2" t="inlineStr"/>
+      <c r="V117" s="2" t="inlineStr"/>
+      <c r="W117" s="2" t="inlineStr"/>
+      <c r="X117" s="2" t="inlineStr"/>
+      <c r="Y117" s="2" t="inlineStr"/>
+      <c r="Z117" s="2" t="inlineStr"/>
+      <c r="AA117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Wine &amp; Food Kiev</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Wine &amp; Food Kiev</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>55443</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Kyiv</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Kyiv City</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>13 Shovkovychna Street</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>01021</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>https://winefood.ua</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr"/>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr"/>
+      <c r="M118" s="2" t="inlineStr"/>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>wineandfood.kiev@gmail.com</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr"/>
+      <c r="P118" s="2" t="inlineStr"/>
+      <c r="Q118" s="2" t="inlineStr"/>
+      <c r="R118" s="2" t="inlineStr"/>
+      <c r="S118" s="2" t="inlineStr"/>
+      <c r="T118" s="2" t="inlineStr"/>
+      <c r="U118" s="2" t="inlineStr"/>
+      <c r="V118" s="2" t="inlineStr"/>
+      <c r="W118" s="2" t="inlineStr"/>
+      <c r="X118" s="2" t="inlineStr"/>
+      <c r="Y118" s="2" t="inlineStr"/>
+      <c r="Z118" s="2" t="inlineStr"/>
+      <c r="AA118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Pivasov</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Pivasov</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>65328</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>Odesa</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Odes'ka oblast, Odes'ka city council</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>49 Henerala Petrova Street</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>65000</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>https://pivasov.ua</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr"/>
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="2" t="inlineStr"/>
+      <c r="M119" s="2" t="inlineStr"/>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>office@pivasov.ua</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr"/>
+      <c r="P119" s="2" t="inlineStr"/>
+      <c r="Q119" s="2" t="inlineStr"/>
+      <c r="R119" s="2" t="inlineStr"/>
+      <c r="S119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/pivasov.ua</t>
+        </is>
+      </c>
+      <c r="T119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pivasov.ua/</t>
+        </is>
+      </c>
+      <c r="U119" s="2" t="inlineStr"/>
+      <c r="V119" s="2" t="inlineStr"/>
+      <c r="W119" s="2" t="inlineStr"/>
+      <c r="X119" s="2" t="inlineStr"/>
+      <c r="Y119" s="2" t="inlineStr"/>
+      <c r="Z119" s="2" t="inlineStr"/>
+      <c r="AA119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Vino &amp; Vino</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Vino &amp; Vino</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>49522</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Kyiv</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Kyiv, Kyiv City</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>47 Sichovykh Striltsiv Street</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>02000</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>https://vinovino.com.ua</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr"/>
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr"/>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>info@vinovino.com.ua</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>+380 800 207 629</t>
+        </is>
+      </c>
+      <c r="P120" s="2" t="inlineStr"/>
+      <c r="Q120" s="2" t="inlineStr"/>
+      <c r="R120" s="2" t="inlineStr"/>
+      <c r="S120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinovino.ukraine/</t>
+        </is>
+      </c>
+      <c r="T120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinovino.com.ua</t>
+        </is>
+      </c>
+      <c r="U120" s="2" t="inlineStr"/>
+      <c r="V120" s="2" t="inlineStr"/>
+      <c r="W120" s="2" t="inlineStr"/>
+      <c r="X120" s="2" t="inlineStr"/>
+      <c r="Y120" s="2" t="inlineStr"/>
+      <c r="Z120" s="2" t="inlineStr"/>
+      <c r="AA120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Vinhol Velvet</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Vinhol Velvet</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>51810</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>Odessa</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Odeska</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>St. New 1-b, Oksamitnoe</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>65031</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>https://winehall.prom.ua</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr"/>
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="2" t="inlineStr"/>
+      <c r="M121" s="2" t="inlineStr"/>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>winehall2006@gmail.com</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr"/>
+      <c r="P121" s="2" t="inlineStr"/>
+      <c r="Q121" s="2" t="inlineStr"/>
+      <c r="R121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winehall-oksamytne/</t>
+        </is>
+      </c>
+      <c r="S121" s="2" t="inlineStr"/>
+      <c r="T121" s="2" t="inlineStr"/>
+      <c r="U121" s="2" t="inlineStr"/>
+      <c r="V121" s="2" t="inlineStr"/>
+      <c r="W121" s="2" t="inlineStr">
+        <is>
+          <t>Tintulov Yuriy</t>
+        </is>
+      </c>
+      <c r="X121" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Manager</t>
+        </is>
+      </c>
+      <c r="Y121" s="2" t="inlineStr"/>
+      <c r="Z121" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tintulov-yuriy-b79ab515a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Vinhol Velvet</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Vinhol Velvet</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>51810</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Odessa</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Odeska</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>St. New 1-b, Oksamitnoe</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>65031</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>https://winehall.prom.ua</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr"/>
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="inlineStr"/>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>winehall2006@gmail.com</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr"/>
+      <c r="P122" s="2" t="inlineStr"/>
+      <c r="Q122" s="2" t="inlineStr"/>
+      <c r="R122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winehall-oksamytne/</t>
+        </is>
+      </c>
+      <c r="S122" s="2" t="inlineStr"/>
+      <c r="T122" s="2" t="inlineStr"/>
+      <c r="U122" s="2" t="inlineStr"/>
+      <c r="V122" s="2" t="inlineStr"/>
+      <c r="W122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dmitry </t>
+        </is>
+      </c>
+      <c r="X122" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y122" s="2" t="inlineStr"/>
+      <c r="Z122" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Vinhol Velvet</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Vinhol Velvet</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>51810</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Odessa</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Odeska</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>St. New 1-b, Oksamitnoe</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>65031</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>https://winehall.prom.ua</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr"/>
+      <c r="K123" s="2" t="inlineStr"/>
+      <c r="L123" s="2" t="inlineStr"/>
+      <c r="M123" s="2" t="inlineStr"/>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>winehall2006@gmail.com</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr"/>
+      <c r="P123" s="2" t="inlineStr"/>
+      <c r="Q123" s="2" t="inlineStr"/>
+      <c r="R123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winehall-oksamytne/</t>
+        </is>
+      </c>
+      <c r="S123" s="2" t="inlineStr"/>
+      <c r="T123" s="2" t="inlineStr"/>
+      <c r="U123" s="2" t="inlineStr"/>
+      <c r="V123" s="2" t="inlineStr"/>
+      <c r="W123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Constantine </t>
+        </is>
+      </c>
+      <c r="X123" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y123" s="2" t="inlineStr"/>
+      <c r="Z123" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Invino Direct</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Invino Direct</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>65106</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Kharkiv</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Kharkivs'ka oblast, Kharkivs'ka city council</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>54 Myronosytska Street</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>61000</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>https://invino.com.ua</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr"/>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr"/>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>ishop@invino.com.ua</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr"/>
+      <c r="P124" s="2" t="inlineStr"/>
+      <c r="Q124" s="2" t="inlineStr"/>
+      <c r="R124" s="2" t="inlineStr"/>
+      <c r="S124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/invinomir/</t>
+        </is>
+      </c>
+      <c r="T124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/invino_profi/</t>
+        </is>
+      </c>
+      <c r="U124" s="2" t="inlineStr"/>
+      <c r="V124" s="2" t="inlineStr"/>
+      <c r="W124" s="2" t="inlineStr"/>
+      <c r="X124" s="2" t="inlineStr"/>
+      <c r="Y124" s="2" t="inlineStr"/>
+      <c r="Z124" s="2" t="inlineStr"/>
+      <c r="AA124" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
